--- a/EdenCampus_PhD/04_results/tables/scenario_comparison_S0_S4.xlsx
+++ b/EdenCampus_PhD/04_results/tables/scenario_comparison_S0_S4.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>121.8</v>
+        <v>122.2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -485,13 +485,13 @@
         <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
         <v>14.7</v>
       </c>
       <c r="I2" t="n">
-        <v>34114.5</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>78.3</v>
       </c>
       <c r="C3" t="n">
-        <v>107.9</v>
+        <v>109</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -513,16 +513,16 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>40.7</v>
       </c>
       <c r="H3" t="n">
         <v>18.3</v>
       </c>
       <c r="I3" t="n">
-        <v>30217.2</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>160.1</v>
+        <v>156.7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -547,13 +547,13 @@
         <v>37.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-32.1</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
         <v>16.3</v>
       </c>
       <c r="I4" t="n">
-        <v>44848.5</v>
+        <v>123.6</v>
       </c>
     </row>
     <row r="5">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>115.9</v>
+        <v>116.3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -575,16 +575,16 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="H5" t="n">
         <v>18.6</v>
       </c>
       <c r="I5" t="n">
-        <v>32489.3</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
         <v>87.40000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>148.2</v>
+        <v>131.4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -606,16 +606,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-32.1</v>
+        <v>44.9</v>
       </c>
       <c r="H6" t="n">
         <v>20.4</v>
       </c>
       <c r="I6" t="n">
-        <v>41537</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
   </sheetData>
